--- a/解题-gpt/结果/问题四_2批次_错峰复用优化.xlsx
+++ b/解题-gpt/结果/问题四_2批次_错峰复用优化.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,11 +577,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UC02</t>
+          <t>UC01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>C-BAT-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>26.19033615606908</v>
       </c>
       <c r="H3" t="n">
-        <v>16.49825141136787</v>
+        <v>42.68858756743695</v>
       </c>
       <c r="I3" t="n">
-        <v>21.79033615606908</v>
+        <v>47.98067231213816</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
@@ -639,21 +639,21 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UC01</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C-BAT-01</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S001-FOD-01,S001-FOD-02,S001-FOD-03</t>
+          <t>S001-FOD-01,S001-FOD-02</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>59.08407992144435</v>
+        <v>35.49285073617485</v>
       </c>
       <c r="H4" t="n">
-        <v>75.58233133281222</v>
+        <v>50.71669070780122</v>
       </c>
       <c r="I4" t="n">
-        <v>80.87441607751343</v>
+        <v>56.50308623498314</v>
       </c>
       <c r="J4" t="n">
         <v>120</v>
@@ -682,13 +682,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.914498008428869</v>
+        <v>1.048835444247772</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7606877489463914</v>
+        <v>0.7669254568338284</v>
       </c>
       <c r="N4" t="n">
-        <v>22.53072017693587</v>
+        <v>13.38328176860038</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -701,21 +701,21 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UC01</t>
+          <t>UA02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C-BAT-01</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -725,32 +725,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S001-HYG-01,S001-HYG-02</t>
+          <t>S001-FOD-03</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>111.3818220273667</v>
+        <v>55.37837351819476</v>
       </c>
       <c r="H5" t="n">
-        <v>126.7800734387346</v>
+        <v>69.60221348982112</v>
       </c>
       <c r="I5" t="n">
-        <v>132.0721581834358</v>
+        <v>75.38860901700306</v>
       </c>
       <c r="J5" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.835475722612836</v>
+        <v>1.014245103020607</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7705655346733955</v>
+        <v>0.7746121993287539</v>
       </c>
       <c r="N5" t="n">
-        <v>22.17402235901627</v>
+        <v>13.21673568121033</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -763,103 +763,103 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>B-BAT-04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S002-WAT-01,S002-MED-01</t>
+          <t>S001-HYG-01,S001-HYG-02</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>132.0721581834358</v>
+        <v>88.36859904779647</v>
       </c>
       <c r="H6" t="n">
-        <v>153.4904796945144</v>
+        <v>102.7414926041643</v>
       </c>
       <c r="I6" t="n">
-        <v>165.5108012055931</v>
+        <v>107.6769417160876</v>
       </c>
       <c r="J6" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>2.421359503464448</v>
+        <v>0.8736555559417358</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4619201103412338</v>
+        <v>0.7815861110145661</v>
       </c>
       <c r="N6" t="n">
-        <v>19.9917309426066</v>
+        <v>17.42084568180142</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>G2</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>132.0721581834358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UC02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>C-BAT-02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S006-WAT-01,S006-WAT-02</t>
+          <t>S002-WAT-01,S002-WAT-02,S002-WAT-03,S002-WAT-04,S002-MED-01</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
       <c r="H7" t="n">
-        <v>146.7498211400937</v>
+        <v>131.3777200393997</v>
       </c>
       <c r="I7" t="n">
-        <v>152.1353729856406</v>
+        <v>141.7314983627118</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -868,13 +868,13 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.087081446911481</v>
+        <v>5.151810515822099</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7282296382721298</v>
+        <v>0.3560236855222376</v>
       </c>
       <c r="N7" t="n">
-        <v>18.96225489436069</v>
+        <v>37.14358913391919</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -882,26 +882,26 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S006-WAT-03,S006-MED-01</t>
+          <t>S006-WAT-01,S006-MED-01</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
       <c r="H8" t="n">
-        <v>146.7498211400937</v>
+        <v>123.2382238156432</v>
       </c>
       <c r="I8" t="n">
-        <v>152.1353729856406</v>
+        <v>129.5073948040877</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -930,13 +930,13 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9613264853346692</v>
+        <v>1.106805665390136</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7596683786663327</v>
+        <v>0.7540431854688587</v>
       </c>
       <c r="N8" t="n">
-        <v>18.05402461630594</v>
+        <v>13.66239764817473</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>152.1353729856406</v>
+        <v>107.6769417160876</v>
       </c>
       <c r="H9" t="n">
-        <v>169.8055983948857</v>
+        <v>125.3471671253328</v>
       </c>
       <c r="I9" t="n">
-        <v>178.2211571374642</v>
+        <v>133.7627258679112</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -1006,26 +1006,26 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UC02</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>153.8624943395049</v>
+        <v>107.6769417160876</v>
       </c>
       <c r="H10" t="n">
-        <v>172.0479219397098</v>
+        <v>124.6944451313508</v>
       </c>
       <c r="I10" t="n">
-        <v>180.4065162065814</v>
+        <v>132.4607263243918</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
@@ -1054,13 +1054,13 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>2.910315433999106</v>
+        <v>1.424415898434041</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6362105707501118</v>
+        <v>0.6438960253914898</v>
       </c>
       <c r="N10" t="n">
-        <v>27.0257293895793</v>
+        <v>21.39855926646807</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1068,12 +1068,12 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
       <c r="H11" t="n">
-        <v>150.1128950430252</v>
+        <v>125.717678575677</v>
       </c>
       <c r="I11" t="n">
-        <v>158.9025207915035</v>
+        <v>134.5073043241554</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -1130,26 +1130,26 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UC01</t>
+          <t>UA03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C-BAT-04</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>158.2624943395049</v>
+        <v>107.6769417160876</v>
       </c>
       <c r="H12" t="n">
-        <v>179.6826162221925</v>
+        <v>129.9154756892241</v>
       </c>
       <c r="I12" t="n">
-        <v>191.1562381048801</v>
+        <v>142.8230096623606</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
@@ -1178,13 +1178,13 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>4.320888294761101</v>
+        <v>2.471325003399136</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4598889631548624</v>
+        <v>0.4508166659113031</v>
       </c>
       <c r="N12" t="n">
-        <v>33.39289855274107</v>
+        <v>20.23230557192176</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1192,16 +1192,16 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
       <c r="H13" t="n">
-        <v>153.2888302130111</v>
+        <v>128.8936137456629</v>
       </c>
       <c r="I13" t="n">
-        <v>165.2536133536976</v>
+        <v>140.8583968863494</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -1254,16 +1254,16 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A-BAT-04</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S002-WAT-02</t>
+          <t>S006-WAT-02</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>132.0721581834358</v>
+        <v>129.5073948040877</v>
       </c>
       <c r="H14" t="n">
-        <v>152.4904796945144</v>
+        <v>144.0686769036433</v>
       </c>
       <c r="I14" t="n">
-        <v>164.5108012055931</v>
+        <v>150.3378478920878</v>
       </c>
       <c r="J14" t="n">
         <v>60</v>
@@ -1302,13 +1302,13 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>2.38786730414774</v>
+        <v>1.092476706316119</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4693628213005021</v>
+        <v>0.757227398596418</v>
       </c>
       <c r="N14" t="n">
-        <v>19.83047220515579</v>
+        <v>13.59340636374428</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1316,12 +1316,12 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1335,27 +1335,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>A-BAT-06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S002-WAT-03</t>
+          <t>S006-WAT-03</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>158.9025207915035</v>
+        <v>134.5073043241554</v>
       </c>
       <c r="H15" t="n">
-        <v>179.3208423025822</v>
+        <v>149.068586423711</v>
       </c>
       <c r="I15" t="n">
-        <v>191.3411638136608</v>
+        <v>155.3377574121555</v>
       </c>
       <c r="J15" t="n">
         <v>60</v>
@@ -1364,13 +1364,13 @@
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>2.38786730414774</v>
+        <v>1.092476706316119</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4693628213005021</v>
+        <v>0.757227398596418</v>
       </c>
       <c r="N15" t="n">
-        <v>19.83047220515579</v>
+        <v>13.59340636374428</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1378,46 +1378,46 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A-BAT-06</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S002-WAT-04</t>
+          <t>S007-MED-01</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>164.5108012055931</v>
+        <v>132.4607263243918</v>
       </c>
       <c r="H16" t="n">
-        <v>184.9291227166718</v>
+        <v>149.1309517336369</v>
       </c>
       <c r="I16" t="n">
-        <v>196.9494442277504</v>
+        <v>157.5465104762154</v>
       </c>
       <c r="J16" t="n">
         <v>60</v>
@@ -1426,13 +1426,13 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>2.38786730414774</v>
+        <v>1.278665737006417</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4693628213005021</v>
+        <v>0.6803335657483958</v>
       </c>
       <c r="N16" t="n">
-        <v>19.83047220515579</v>
+        <v>20.34591921171301</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1440,61 +1440,61 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UC02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S007-MED-01</t>
+          <t>S003-WAT-01,S003-WAT-02,S003-WAT-03,S003-WAT-04,S003-MED-01</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>152.1353729856406</v>
+        <v>141.7314983627118</v>
       </c>
       <c r="H17" t="n">
-        <v>168.8055983948857</v>
+        <v>167.9797523225136</v>
       </c>
       <c r="I17" t="n">
-        <v>177.2211571374642</v>
+        <v>181.0793396156487</v>
       </c>
       <c r="J17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.278665737006417</v>
+        <v>5.440500810633867</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6803335657483958</v>
+        <v>0.3199373986707666</v>
       </c>
       <c r="N17" t="n">
-        <v>20.34591921171301</v>
+        <v>38.44670504800009</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1502,16 +1502,16 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UC02</t>
+          <t>UC01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1521,27 +1521,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>C-BAT-01</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S003-WAT-01,S003-WAT-02,S003-WAT-03,S003-WAT-04,S003-MED-01</t>
+          <t>S008-WAT-01,S008-WAT-02,S008-MED-01</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>180.4065162065814</v>
+        <v>159.3068172624159</v>
       </c>
       <c r="H18" t="n">
-        <v>206.6547701663832</v>
+        <v>182.0495836000306</v>
       </c>
       <c r="I18" t="n">
-        <v>219.7543574595183</v>
+        <v>193.7310166043121</v>
       </c>
       <c r="J18" t="n">
         <v>120</v>
@@ -1550,13 +1550,13 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>5.440500810633867</v>
+        <v>4.880456740806956</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3199373986707666</v>
+        <v>0.3899429073991305</v>
       </c>
       <c r="N18" t="n">
-        <v>38.44670504800009</v>
+        <v>35.91872834392029</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1564,16 +1564,16 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>B-BAT-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>177.2211571374642</v>
+        <v>133.7627258679112</v>
       </c>
       <c r="H19" t="n">
-        <v>198.0387637629052</v>
+        <v>154.5803324933522</v>
       </c>
       <c r="I19" t="n">
-        <v>209.4681481661239</v>
+        <v>166.0097168965709</v>
       </c>
       <c r="J19" t="n">
         <v>120</v>
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1659,13 +1659,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>178.2211571374642</v>
+        <v>157.5465104762154</v>
       </c>
       <c r="H20" t="n">
-        <v>199.0387637629052</v>
+        <v>178.3641171016564</v>
       </c>
       <c r="I20" t="n">
-        <v>210.4681481661239</v>
+        <v>189.7935015048752</v>
       </c>
       <c r="J20" t="n">
         <v>120</v>
@@ -1688,12 +1688,12 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1712,22 +1712,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S008-WAT-01,S008-MED-01</t>
+          <t>S002-FOD-01,S002-FOD-02</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>175.1194637677136</v>
+        <v>150.7242473003654</v>
       </c>
       <c r="H21" t="n">
-        <v>197.8821202200923</v>
+        <v>172.1425688114441</v>
       </c>
       <c r="I21" t="n">
-        <v>211.3038877835822</v>
+        <v>184.1628903225227</v>
       </c>
       <c r="J21" t="n">
         <v>120</v>
@@ -1736,13 +1736,13 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>2.660432042052936</v>
+        <v>2.409990591769786</v>
       </c>
       <c r="M21" t="n">
-        <v>0.408792879543792</v>
+        <v>0.4644465351622699</v>
       </c>
       <c r="N21" t="n">
-        <v>21.14282094321784</v>
+        <v>19.93699173815082</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1750,12 +1750,12 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1769,27 +1769,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>S002-FOD-01,S002-FOD-02</t>
+          <t>S015-MED-01</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>183.0939764658342</v>
+        <v>158.698759998486</v>
       </c>
       <c r="H22" t="n">
-        <v>204.5122979769129</v>
+        <v>178.6381019783232</v>
       </c>
       <c r="I22" t="n">
-        <v>216.5326194879916</v>
+        <v>190.4627772914936</v>
       </c>
       <c r="J22" t="n">
         <v>120</v>
@@ -1798,13 +1798,13 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>2.409990591769786</v>
+        <v>1.976874086653691</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4644465351622699</v>
+        <v>0.5606946474102907</v>
       </c>
       <c r="N22" t="n">
-        <v>19.93699173815082</v>
+        <v>17.85161597277703</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="23">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UA02</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1831,27 +1831,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A-BAT-04</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>S008-WAT-02</t>
+          <t>S006-FOD-01</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>191.3411638136608</v>
+        <v>164.1800279510707</v>
       </c>
       <c r="H23" t="n">
-        <v>213.1038202660396</v>
+        <v>178.7413100506263</v>
       </c>
       <c r="I23" t="n">
-        <v>226.5255878295294</v>
+        <v>185.0104810390709</v>
       </c>
       <c r="J23" t="n">
         <v>120</v>
@@ -1860,13 +1860,13 @@
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>2.623902934018422</v>
+        <v>1.066023243410243</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4169104591070174</v>
+        <v>0.7631059459088348</v>
       </c>
       <c r="N23" t="n">
-        <v>20.96694005268129</v>
+        <v>13.46603783864191</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="24">
@@ -1883,37 +1883,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UC01</t>
+          <t>UA02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>A-BAT-06</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S015-MED-01</t>
+          <t>S007-FOD-01</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>212.9465742609492</v>
+        <v>183.0655507330907</v>
       </c>
       <c r="H24" t="n">
-        <v>232.4612772358759</v>
+        <v>200.9951710411154</v>
       </c>
       <c r="I24" t="n">
-        <v>243.4539802108025</v>
+        <v>210.6701246824734</v>
       </c>
       <c r="J24" t="n">
         <v>120</v>
@@ -1922,13 +1922,13 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>3.56316577275202</v>
+        <v>1.571297495086422</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5546042784059975</v>
+        <v>0.6508227788696839</v>
       </c>
       <c r="N24" t="n">
-        <v>29.97262327978342</v>
+        <v>15.89883979115685</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="25">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UA03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>S006-FOD-01</t>
+          <t>S010-FOD-01</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>196.9494442277504</v>
+        <v>184.1628903225227</v>
       </c>
       <c r="H25" t="n">
-        <v>211.510726327306</v>
+        <v>201.5077363214992</v>
       </c>
       <c r="I25" t="n">
-        <v>217.7798973157505</v>
+        <v>210.6013600982534</v>
       </c>
       <c r="J25" t="n">
         <v>120</v>
@@ -1984,13 +1984,13 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.066023243410243</v>
+        <v>1.581530554767664</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7631059459088348</v>
+        <v>0.6485487656071858</v>
       </c>
       <c r="N25" t="n">
-        <v>13.46603783864191</v>
+        <v>15.94811007851097</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="26">
@@ -2007,37 +2007,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>S007-FOD-01</t>
+          <t>S012-FOD-01</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>211.3038877835822</v>
+        <v>166.0097168965709</v>
       </c>
       <c r="H26" t="n">
-        <v>229.2335080916068</v>
+        <v>185.1931288302275</v>
       </c>
       <c r="I26" t="n">
-        <v>238.9084617329649</v>
+        <v>196.045540763884</v>
       </c>
       <c r="J26" t="n">
         <v>120</v>
@@ -2046,13 +2046,13 @@
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.571297495086422</v>
+        <v>1.971677737898548</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6508227788696839</v>
+        <v>0.5070805655253631</v>
       </c>
       <c r="N26" t="n">
-        <v>15.89883979115685</v>
+        <v>25.35100588482284</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="27">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2079,27 +2079,27 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>A-BAT-06</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>S010-FOD-01</t>
+          <t>S013-FOD-01</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>216.7799164329062</v>
+        <v>196.282286414301</v>
       </c>
       <c r="H27" t="n">
-        <v>234.1247624318827</v>
+        <v>213.3230232738904</v>
       </c>
       <c r="I27" t="n">
-        <v>243.2183862086369</v>
+        <v>222.1126490223688</v>
       </c>
       <c r="J27" t="n">
         <v>120</v>
@@ -2108,13 +2108,13 @@
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.581530554767664</v>
+        <v>1.575202255282084</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6485487656071858</v>
+        <v>0.6499550543817592</v>
       </c>
       <c r="N27" t="n">
-        <v>15.94811007851097</v>
+        <v>15.91764048839522</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="28">
@@ -2141,27 +2141,27 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>S012-FOD-01</t>
+          <t>S014-FOD-01</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>209.4681481661239</v>
+        <v>189.7935015048752</v>
       </c>
       <c r="H28" t="n">
-        <v>228.6515600997805</v>
+        <v>208.5071430843109</v>
       </c>
       <c r="I28" t="n">
-        <v>239.503972033437</v>
+        <v>218.9688957748577</v>
       </c>
       <c r="J28" t="n">
         <v>120</v>
@@ -2170,13 +2170,13 @@
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.971677737898548</v>
+        <v>1.607789512414177</v>
       </c>
       <c r="M28" t="n">
-        <v>0.5070805655253631</v>
+        <v>0.5980526218964557</v>
       </c>
       <c r="N28" t="n">
-        <v>25.35100588482284</v>
+        <v>22.72292425632461</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="29">
@@ -2193,52 +2193,52 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UC02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>C-BAT-03</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>S013-FOD-01</t>
+          <t>S005-WAT-01,S005-WAT-02,S005-WAT-03,S005-MED-01</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>210.4681481661239</v>
+        <v>181.0793396156487</v>
       </c>
       <c r="H29" t="n">
-        <v>226.1620238305468</v>
+        <v>201.7152909566813</v>
       </c>
       <c r="I29" t="n">
-        <v>233.6047883838585</v>
+        <v>210.0634089643804</v>
       </c>
       <c r="J29" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.309771480726076</v>
+        <v>3.517681856451785</v>
       </c>
       <c r="M29" t="n">
-        <v>0.672557129818481</v>
+        <v>0.5602897679435269</v>
       </c>
       <c r="N29" t="n">
-        <v>20.57057180524388</v>
+        <v>29.76731393537263</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="30">
@@ -2255,52 +2255,52 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UC02</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>C-BAT-04</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>S014-FOD-01</t>
+          <t>S009-WAT-01,S009-MED-01</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>224.5491366576212</v>
+        <v>198.4765188777128</v>
       </c>
       <c r="H30" t="n">
-        <v>244.7838357625593</v>
+        <v>217.2413540328317</v>
       </c>
       <c r="I30" t="n">
-        <v>256.2907015341641</v>
+        <v>226.6198558546173</v>
       </c>
       <c r="J30" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="K30" t="b">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>3.492318945036377</v>
+        <v>1.8710546231918</v>
       </c>
       <c r="M30" t="n">
-        <v>0.5634601318704529</v>
+        <v>0.5842100837351556</v>
       </c>
       <c r="N30" t="n">
-        <v>29.65282857134476</v>
+        <v>17.34211485240496</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="31">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UA03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2327,27 +2327,27 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>A-BAT-02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>S005-WAT-01,S005-MED-01</t>
+          <t>S011-WAT-01,S011-MED-01</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>231.2459351543924</v>
+        <v>210.6013600982534</v>
       </c>
       <c r="H31" t="n">
-        <v>250.0287494359932</v>
+        <v>225.4340368268726</v>
       </c>
       <c r="I31" t="n">
-        <v>259.3863414953718</v>
+        <v>230.8604913332695</v>
       </c>
       <c r="J31" t="n">
         <v>180</v>
@@ -2356,13 +2356,13 @@
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1.779919328040352</v>
+        <v>0.974739867166567</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6044623715465884</v>
+        <v>0.7833911406296518</v>
       </c>
       <c r="N31" t="n">
-        <v>16.90331528315725</v>
+        <v>13.02652528635754</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2370,46 +2370,46 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UA02</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>A-BAT-02</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>S009-WAT-01,S009-MED-01</t>
+          <t>S003-FOD-01,S003-FOD-02</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>232.4467087268</v>
+        <v>217.0872598136295</v>
       </c>
       <c r="H32" t="n">
-        <v>251.2115438819189</v>
+        <v>238.4947971020593</v>
       </c>
       <c r="I32" t="n">
-        <v>260.5900457037045</v>
+        <v>250.6365566127114</v>
       </c>
       <c r="J32" t="n">
         <v>180</v>
@@ -2418,13 +2418,13 @@
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.8710546231918</v>
+        <v>2.171939602406073</v>
       </c>
       <c r="M32" t="n">
-        <v>0.5842100837351556</v>
+        <v>0.4570150993984818</v>
       </c>
       <c r="N32" t="n">
-        <v>17.34211485240496</v>
+        <v>26.79734157293274</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2432,46 +2432,46 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UA02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>S011-WAT-01,S011-MED-01</t>
+          <t>S002-HYG-01</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>237.7619064748782</v>
+        <v>210.6701246824734</v>
       </c>
       <c r="H33" t="n">
-        <v>251.8120421385137</v>
+        <v>231.088446193552</v>
       </c>
       <c r="I33" t="n">
-        <v>256.4559555799269</v>
+        <v>243.1087677046307</v>
       </c>
       <c r="J33" t="n">
         <v>180</v>
@@ -2480,13 +2480,13 @@
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>0.845945507122666</v>
+        <v>2.306810552860246</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7885136232193335</v>
+        <v>0.4873754326977231</v>
       </c>
       <c r="N33" t="n">
-        <v>17.22071755144147</v>
+        <v>19.440198958216</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="34">
@@ -2503,37 +2503,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UC01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>C-BAT-02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>S003-FOD-01,S003-FOD-02</t>
+          <t>S004-FOD-01</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>239.503972033437</v>
+        <v>193.7310166043121</v>
       </c>
       <c r="H34" t="n">
-        <v>260.9115093218669</v>
+        <v>214.7495914671633</v>
       </c>
       <c r="I34" t="n">
-        <v>273.053268832519</v>
+        <v>226.8358329966813</v>
       </c>
       <c r="J34" t="n">
         <v>180</v>
@@ -2542,13 +2542,13 @@
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>2.171939602406073</v>
+        <v>4.403269646749423</v>
       </c>
       <c r="M34" t="n">
-        <v>0.4570150993984818</v>
+        <v>0.4495912941563222</v>
       </c>
       <c r="N34" t="n">
-        <v>26.79734157293274</v>
+        <v>33.7647588221328</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="35">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2575,27 +2575,27 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>S005-WAT-02</t>
+          <t>S006-HYG-01</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>238.9084617329649</v>
+        <v>226.5494701767644</v>
       </c>
       <c r="H35" t="n">
-        <v>256.6912760145656</v>
+        <v>241.11075227632</v>
       </c>
       <c r="I35" t="n">
-        <v>266.0488680739442</v>
+        <v>247.3799232647645</v>
       </c>
       <c r="J35" t="n">
         <v>180</v>
@@ -2604,13 +2604,13 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1.756036387465134</v>
+        <v>1.057798217128584</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6097696916744146</v>
+        <v>0.7649337295269814</v>
       </c>
       <c r="N35" t="n">
-        <v>16.78832334705435</v>
+        <v>13.42643586024874</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="36">
@@ -2627,37 +2627,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UC02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A-BAT-04</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>S005-WAT-03</t>
+          <t>S007-HYG-01</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>247.4925278822107</v>
+        <v>219.5260446636488</v>
       </c>
       <c r="H36" t="n">
-        <v>265.2753421638115</v>
+        <v>237.4747804851956</v>
       </c>
       <c r="I36" t="n">
-        <v>274.63293422319</v>
+        <v>246.6915163067423</v>
       </c>
       <c r="J36" t="n">
         <v>180</v>
@@ -2666,13 +2666,13 @@
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>1.756036387465134</v>
+        <v>2.845453629675534</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6097696916744146</v>
+        <v>0.6443182962905583</v>
       </c>
       <c r="N36" t="n">
-        <v>16.78832334705435</v>
+        <v>26.73295041172984</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="37">
@@ -2689,37 +2689,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>A-BAT-05</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>S002-HYG-01</t>
+          <t>S008-FOD-01</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>259.3863414953718</v>
+        <v>221.3965466487069</v>
       </c>
       <c r="H37" t="n">
-        <v>279.8046630064504</v>
+        <v>240.9065747722906</v>
       </c>
       <c r="I37" t="n">
-        <v>291.8249845175291</v>
+        <v>252.0757140069854</v>
       </c>
       <c r="J37" t="n">
         <v>180</v>
@@ -2728,13 +2728,13 @@
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>2.306810552860246</v>
+        <v>2.113150583946663</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4873754326977231</v>
+        <v>0.4717123540133343</v>
       </c>
       <c r="N37" t="n">
-        <v>19.440198958216</v>
+        <v>26.37275421739256</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="38">
@@ -2751,37 +2751,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UA02</t>
+          <t>UC01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>A-BAT-06</t>
+          <t>C-BAT-01</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>S004-FOD-01</t>
+          <t>S015-WAT-01</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>260.5900457037045</v>
+        <v>229.6497449482323</v>
       </c>
       <c r="H38" t="n">
-        <v>282.5592222576877</v>
+        <v>249.164447923159</v>
       </c>
       <c r="I38" t="n">
-        <v>296.1401765894486</v>
+        <v>260.1571508980856</v>
       </c>
       <c r="J38" t="n">
         <v>180</v>
@@ -2790,13 +2790,13 @@
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>2.494804901151978</v>
+        <v>3.686771208193226</v>
       </c>
       <c r="M38" t="n">
-        <v>0.445598910855116</v>
+        <v>0.5391535989758467</v>
       </c>
       <c r="N38" t="n">
-        <v>20.34535693147248</v>
+        <v>30.53056448142775</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="39">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>UA03</t>
+          <t>UA01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2823,42 +2823,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>A-BAT-06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>S006-HYG-01</t>
+          <t>S003-HYG-01</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>276.289656778529</v>
+        <v>226.6198558546173</v>
       </c>
       <c r="H39" t="n">
-        <v>290.8509388780845</v>
+        <v>249.0443557933121</v>
       </c>
       <c r="I39" t="n">
-        <v>297.1201098665291</v>
+        <v>263.2030779542291</v>
       </c>
       <c r="J39" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>1.057798217128584</v>
+        <v>2.412427120788479</v>
       </c>
       <c r="M39" t="n">
-        <v>0.7649337295269814</v>
+        <v>0.4639050842692268</v>
       </c>
       <c r="N39" t="n">
-        <v>13.42643586024874</v>
+        <v>19.94872317416675</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="40">
@@ -2875,52 +2875,52 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UC02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>C-BAT-03</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>S007-HYG-01</t>
+          <t>S004-HYG-01</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>256.4559555799269</v>
+        <v>246.6915163067423</v>
       </c>
       <c r="H40" t="n">
-        <v>273.1261809891721</v>
+        <v>267.7100911695936</v>
       </c>
       <c r="I40" t="n">
-        <v>281.5417397317505</v>
+        <v>279.7963326991116</v>
       </c>
       <c r="J40" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>1.304041604369885</v>
+        <v>4.375001305345046</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6739895989075286</v>
+        <v>0.4531248368318692</v>
       </c>
       <c r="N40" t="n">
-        <v>20.52918936489361</v>
+        <v>33.63715866996027</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="41">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>UA01</t>
+          <t>UA03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2947,42 +2947,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A-BAT-02</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>S008-FOD-01</t>
+          <t>S005-FOD-01</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>277.9321605561094</v>
+        <v>238.030289510764</v>
       </c>
       <c r="H41" t="n">
-        <v>299.6948170084882</v>
+        <v>255.8131037923647</v>
       </c>
       <c r="I41" t="n">
-        <v>313.116584571978</v>
+        <v>265.1706958517433</v>
       </c>
       <c r="J41" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>2.556464580723934</v>
+        <v>1.711944804864733</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4318967598391258</v>
+        <v>0.6195678211411705</v>
       </c>
       <c r="N41" t="n">
-        <v>20.64223687015227</v>
+        <v>16.57603054194131</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="42">
@@ -2999,52 +2999,52 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>UC02</t>
+          <t>UB01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>B-BAT-04</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>S015-WAT-01</t>
+          <t>S008-HYG-01</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>258.2010625075184</v>
+        <v>250.6365566127114</v>
       </c>
       <c r="H42" t="n">
-        <v>277.7157654824451</v>
+        <v>270.1465847362951</v>
       </c>
       <c r="I42" t="n">
-        <v>288.7084684573717</v>
+        <v>281.3157239709898</v>
       </c>
       <c r="J42" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>3.686771208193226</v>
+        <v>2.080451140464154</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5391535989758467</v>
+        <v>0.4798872148839615</v>
       </c>
       <c r="N42" t="n">
-        <v>30.53056448142775</v>
+        <v>26.13659157001889</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="43">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>UA04</t>
+          <t>UA02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3071,27 +3071,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A-BAT-03</t>
+          <t>A-BAT-02</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>S003-HYG-01</t>
+          <t>S009-FOD-01</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>291.8249845175291</v>
+        <v>243.887016619627</v>
       </c>
       <c r="H43" t="n">
-        <v>314.2494844562239</v>
+        <v>261.6518517747459</v>
       </c>
       <c r="I43" t="n">
-        <v>328.4082066171409</v>
+        <v>271.0303535965315</v>
       </c>
       <c r="J43" t="n">
         <v>240</v>
@@ -3100,13 +3100,13 @@
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>2.412427120788479</v>
+        <v>1.797687027182534</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4639050842692268</v>
+        <v>0.6005139939594369</v>
       </c>
       <c r="N43" t="n">
-        <v>19.94872317416675</v>
+        <v>16.9888634642122</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="44">
@@ -3123,37 +3123,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UC01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>C-BAT-02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>S004-HYG-01</t>
+          <t>S011-FOD-01</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>273.053268832519</v>
+        <v>260.6005918188141</v>
       </c>
       <c r="H44" t="n">
-        <v>292.87087545796</v>
+        <v>274.56066037723</v>
       </c>
       <c r="I44" t="n">
-        <v>304.3002598611787</v>
+        <v>279.5613956023126</v>
       </c>
       <c r="J44" t="n">
         <v>240</v>
@@ -3162,13 +3162,13 @@
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>2.039725715171945</v>
+        <v>1.681614284379605</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4900685712070139</v>
+        <v>0.7897982144525494</v>
       </c>
       <c r="N44" t="n">
-        <v>25.84246349846404</v>
+        <v>21.47950892254682</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="45">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UB01</t>
+          <t>UB02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3195,27 +3195,27 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>B-BAT-03</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>S005-FOD-01</t>
+          <t>S015-FOD-01</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>281.5417397317505</v>
+        <v>252.0757140069854</v>
       </c>
       <c r="H45" t="n">
-        <v>297.8517726778796</v>
+        <v>270.3430821994349</v>
       </c>
       <c r="I45" t="n">
-        <v>305.7365834017864</v>
+        <v>280.4957837252178</v>
       </c>
       <c r="J45" t="n">
         <v>240</v>
@@ -3224,13 +3224,13 @@
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1.42178203198294</v>
+        <v>1.684852321935074</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6445544920042652</v>
+        <v>0.5787869195162316</v>
       </c>
       <c r="N45" t="n">
-        <v>21.37953689765456</v>
+        <v>23.2794889917533</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
     <row r="46">
@@ -3247,52 +3247,52 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>UB02</t>
+          <t>UA04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>A-BAT-05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>S008-HYG-01</t>
+          <t>S005-HYG-01</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>304.3002598611787</v>
+        <v>247.3799232647645</v>
       </c>
       <c r="H46" t="n">
-        <v>323.8102879847624</v>
+        <v>265.1627375463653</v>
       </c>
       <c r="I46" t="n">
-        <v>334.9794272194571</v>
+        <v>274.5203296057438</v>
       </c>
       <c r="J46" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>2.080451140464154</v>
+        <v>1.698235657333516</v>
       </c>
       <c r="M46" t="n">
-        <v>0.4798872148839615</v>
+        <v>0.6226142983703299</v>
       </c>
       <c r="N46" t="n">
-        <v>26.13659157001889</v>
+        <v>16.51002353530952</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3300,255 +3300,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>132.0721581834358</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>UC01</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>C-BAT-03</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>S009</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>S009-FOD-01</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>273.4266034905859</v>
-      </c>
-      <c r="H47" t="n">
-        <v>290.485552608106</v>
-      </c>
-      <c r="I47" t="n">
-        <v>298.615001725626</v>
-      </c>
-      <c r="J47" t="n">
-        <v>240</v>
-      </c>
-      <c r="K47" t="b">
-        <v>1</v>
-      </c>
-      <c r="L47" t="n">
-        <v>3.136485864490634</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.6079392669386707</v>
-      </c>
-      <c r="N47" t="n">
-        <v>28.04663758277022</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="P47" t="n">
-        <v>132.0721581834358</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>UC02</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>C-BAT-04</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>S011</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>S011-FOD-01</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>288.7084684573717</v>
-      </c>
-      <c r="H48" t="n">
-        <v>302.6685370157876</v>
-      </c>
-      <c r="I48" t="n">
-        <v>307.6692722408702</v>
-      </c>
-      <c r="J48" t="n">
-        <v>240</v>
-      </c>
-      <c r="K48" t="b">
-        <v>1</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1.681614284379605</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.7897982144525494</v>
-      </c>
-      <c r="N48" t="n">
-        <v>21.47950892254682</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="P48" t="n">
-        <v>132.0721581834358</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>UA02</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>A-BAT-04</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>S015</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>S015-FOD-01</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>296.1401765894486</v>
-      </c>
-      <c r="H49" t="n">
-        <v>316.0795185692857</v>
-      </c>
-      <c r="I49" t="n">
-        <v>327.9041938824562</v>
-      </c>
-      <c r="J49" t="n">
-        <v>240</v>
-      </c>
-      <c r="K49" t="b">
-        <v>1</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2.014825572369929</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.5522609839177937</v>
-      </c>
-      <c r="N49" t="n">
-        <v>18.0343453484478</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="P49" t="n">
-        <v>132.0721581834358</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>UA03</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>A-BAT-01</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>S005</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>S005-HYG-01</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>310.5465457267779</v>
-      </c>
-      <c r="H50" t="n">
-        <v>328.3293600083787</v>
-      </c>
-      <c r="I50" t="n">
-        <v>337.6869520677571</v>
-      </c>
-      <c r="J50" t="n">
-        <v>300</v>
-      </c>
-      <c r="K50" t="b">
-        <v>1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1.698235657333516</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.6226142983703299</v>
-      </c>
-      <c r="N50" t="n">
-        <v>16.51002353530952</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="P50" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
     </row>
   </sheetData>
@@ -3614,7 +3366,7 @@
         <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
